--- a/data/再保最低资本2025Q1-0901.xlsx
+++ b/data/再保最低资本2025Q1-0901.xlsx
@@ -1916,6 +1916,9 @@
       <c r="P30" t="n">
         <v>0</v>
       </c>
+      <c r="Q30" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
